--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-12-2025.xlsx
@@ -2189,7 +2189,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£31.63</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£68.43</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
